--- a/artfynd/A 64002-2025 artfynd.xlsx
+++ b/artfynd/A 64002-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54461487</v>
+        <v>102178812</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,50 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>219862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Håkansbo, 1,5 km SO-ut, Upl</t>
+          <t>Tannsjön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663716.7966529995</v>
+        <v>663611</v>
       </c>
       <c r="R2" t="n">
-        <v>6693597.984975527</v>
+        <v>6693673</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,22 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-07-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-07-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,18 +770,24 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Ängsblandskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Karin Wiklund, Thorleif Joelson, Jörgen Sjöström</t>
+          <t>Thorleif Joelson, Jörgen Sjöström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -794,15 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67644775</v>
+        <v>54461483</v>
       </c>
       <c r="B3" t="n">
-        <v>97335</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,41 +809,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222662</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>kalkkärr 1, Upl</t>
+          <t>Håkansbo, 1,3 km SO-ut, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663666.8528947857</v>
+        <v>663593</v>
       </c>
       <c r="R3" t="n">
-        <v>6693615.562626503</v>
+        <v>6693722</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,22 +866,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-07-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-07-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,69 +886,64 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jörgen Sjöström</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jörgen Sjöström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Henry Åkerström, Karin Wiklund, Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67644799</v>
+        <v>54461485</v>
       </c>
       <c r="B4" t="n">
-        <v>97050</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222361</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kalkkärr 2, Upl</t>
+          <t>Håkansbo, 1,3 km SO-ut, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>663666.8528947857</v>
+        <v>663594</v>
       </c>
       <c r="R4" t="n">
-        <v>6693615.562626503</v>
+        <v>6693724</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,22 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-07-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-07-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,54 +990,53 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jörgen Sjöström</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jörgen Sjöström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Henry Åkerström, Karin Wiklund, Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102178812</v>
+        <v>109854655</v>
       </c>
       <c r="B5" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>220075</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1077,21 +1046,21 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tannsjön, Upl</t>
+          <t>Kalkkärr 2, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>663611.1645937416</v>
+        <v>663667</v>
       </c>
       <c r="R5" t="n">
-        <v>6693672.535183853</v>
+        <v>6693616</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,22 +1087,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,56 +1105,42 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Ängsblandskog</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Jörgen Sjöström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Jörgen Sjöström</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102178935</v>
+        <v>67644799</v>
       </c>
       <c r="B6" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>222361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1203,25 +1148,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tannsjön, Upl</t>
+          <t>Kalkkärr 2, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>663611.1645937416</v>
+        <v>663667</v>
       </c>
       <c r="R6" t="n">
-        <v>6693672.535183853</v>
+        <v>6693616</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,22 +1192,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-07-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-07-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,43 +1206,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Ängsblandskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Jörgen Sjöström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Jörgen Sjöström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109854613</v>
+        <v>54461487</v>
       </c>
       <c r="B7" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,16 +1235,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1333,29 +1252,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kalkkärr 2, Upl</t>
+          <t>Håkansbo, 1,5 km SO-ut, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>663666.8528947857</v>
+        <v>663717</v>
       </c>
       <c r="R7" t="n">
-        <v>6693615.562626503</v>
+        <v>6693598</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,22 +1292,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,22 +1306,354 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Karin Wiklund, Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>102178935</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tannsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>663611</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6693673</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Ängsblandskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>67644775</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100171</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222662</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Axag</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Schoenus ferrugineus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>kalkkärr 1, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>663667</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6693616</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-07-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-07-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Jörgen Sjöström</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Jörgen Sjöström</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>109854613</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kalkkärr 2, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>663667</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6693616</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64002-2025 artfynd.xlsx
+++ b/artfynd/A 64002-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102178812</t>
         </is>
       </c>
     </row>
@@ -899,6 +909,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54461483</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54461485</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109854655</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67644799</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1325,6 +1355,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54461487</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102178935</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1544,6 +1584,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67644775</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1654,8 +1699,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109854613</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>